--- a/corpus/xlsx/level-013/template.xlsx
+++ b/corpus/xlsx/level-013/template.xlsx
@@ -46,153 +46,153 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">itl</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">e}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{cu</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">stom</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">er}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">oun</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">t}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{s</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">pac</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ed}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">nabl</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ed}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">iter</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">al}}</t>
+      <t xml:space="preserve">{d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">tit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">le}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">usto</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">mer}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">cou</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">nt}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">spa</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ced}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">enab</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">led}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">lite</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ral}</t>
     </r>
   </si>
 </sst>
